--- a/BAX.xlsx
+++ b/BAX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5068B7-97F7-48A7-8FBF-28F1443C9BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E18739-3326-4EF9-ADC7-D0705492E70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37470" yWindow="1440" windowWidth="27420" windowHeight="18435" activeTab="1" xr2:uid="{8E622A12-89D5-4A8A-9166-8A6C16BEE693}"/>
+    <workbookView xWindow="13160" yWindow="4120" windowWidth="19050" windowHeight="16100" xr2:uid="{8E622A12-89D5-4A8A-9166-8A6C16BEE693}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
   <si>
     <t>Price</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Q424</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -702,9 +705,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E077CF8-8225-4BD7-96A2-952427347746}">
   <dimension ref="H2:L11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>0</v>
       </c>
@@ -712,61 +715,62 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J3" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>510</v>
+        <v>516.46900800000003</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="8:12" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>19380</v>
-      </c>
-    </row>
-    <row r="5" spans="8:12" x14ac:dyDescent="0.2">
+        <v>19625.822304000001</v>
+      </c>
+    </row>
+    <row r="5" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="3">
-        <v>2095</v>
+        <v>2017</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="8:12" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="3">
-        <v>12904</v>
+        <f>842+8621</f>
+        <v>9463</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="8:12" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="8:12" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>30189</v>
-      </c>
-    </row>
-    <row r="10" spans="8:12" x14ac:dyDescent="0.2">
+        <v>27071.822304000001</v>
+      </c>
+    </row>
+    <row r="10" spans="8:12" x14ac:dyDescent="0.25">
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>55</v>
       </c>
@@ -779,19 +783,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3819B66A-6152-46D1-A33C-2DF4BA504DB9}">
   <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="2"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -853,7 +857,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
@@ -878,7 +882,7 @@
       </c>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
@@ -903,7 +907,7 @@
       </c>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
@@ -928,7 +932,7 @@
       </c>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
@@ -953,7 +957,7 @@
       </c>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
@@ -978,7 +982,7 @@
       </c>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
@@ -1003,7 +1007,7 @@
       </c>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
@@ -1028,7 +1032,7 @@
       </c>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
@@ -1053,7 +1057,7 @@
       </c>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>27</v>
       </c>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>28</v>
       </c>
@@ -1103,7 +1107,7 @@
       </c>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
@@ -1128,7 +1132,7 @@
       </c>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
@@ -1167,7 +1171,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>35</v>
       </c>
@@ -1196,7 +1200,7 @@
       </c>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>38</v>
       </c>
@@ -1254,7 +1258,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>37</v>
       </c>
@@ -1278,7 +1282,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -1308,7 +1312,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1338,7 +1342,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1368,7 +1372,7 @@
         <v>-167</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>34</v>
       </c>
@@ -1398,7 +1402,7 @@
         <v>-133</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>33</v>
       </c>
@@ -1428,7 +1432,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -1458,7 +1462,7 @@
         <v>-162</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>-0.32142857142857145</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>1</v>
       </c>
@@ -1510,13 +1514,13 @@
         <v>504</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="T28" s="3">
         <f>+T29-T39</f>
         <v>-10809</v>
       </c>
     </row>
-    <row r="29" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1542,7 +1546,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="30" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
@@ -1568,7 +1572,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="31" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>43</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="32" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>44</v>
       </c>
@@ -1620,7 +1624,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="33" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>45</v>
       </c>
@@ -1646,7 +1650,7 @@
         <v>4314</v>
       </c>
     </row>
-    <row r="34" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>46</v>
       </c>
@@ -1676,7 +1680,7 @@
         <v>11742</v>
       </c>
     </row>
-    <row r="35" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>47</v>
       </c>
@@ -1702,7 +1706,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="36" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>48</v>
       </c>
@@ -1728,7 +1732,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="37" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>49</v>
       </c>
@@ -1758,7 +1762,7 @@
         <v>26312</v>
       </c>
     </row>
-    <row r="38" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -1772,7 +1776,7 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>4</v>
       </c>
@@ -1802,7 +1806,7 @@
         <v>12904</v>
       </c>
     </row>
-    <row r="40" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>50</v>
       </c>
@@ -1828,7 +1832,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="41" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>51</v>
       </c>
@@ -1854,7 +1858,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="42" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>47</v>
       </c>
@@ -1880,7 +1884,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="43" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>52</v>
       </c>
@@ -1906,7 +1910,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="44" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
         <v>53</v>
       </c>
@@ -1932,7 +1936,7 @@
         <v>7708</v>
       </c>
     </row>
-    <row r="45" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>54</v>
       </c>
@@ -1962,7 +1966,7 @@
         <v>26312</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>56</v>
       </c>
@@ -1979,7 +1983,7 @@
         <v>-162</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>57</v>
       </c>
@@ -1995,7 +1999,7 @@
         <v>-2934</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>61</v>
       </c>
@@ -2011,7 +2015,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>62</v>
       </c>
@@ -2027,7 +2031,7 @@
         <v>-87</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>63</v>
       </c>
@@ -2043,7 +2047,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>64</v>
       </c>
@@ -2059,7 +2063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>66</v>
       </c>
@@ -2074,7 +2078,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>29</v>
       </c>
@@ -2090,7 +2094,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
         <v>65</v>
       </c>
@@ -2107,7 +2111,7 @@
         <v>-324</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>60</v>
       </c>
@@ -2124,10 +2128,10 @@
         <v>290</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>59</v>
       </c>
@@ -2143,7 +2147,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>58</v>
       </c>
